--- a/docs/sheets/fire_project_9_advanced_bom_formatted.xlsx
+++ b/docs/sheets/fire_project_9_advanced_bom_formatted.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Luồng căn bản" sheetId="1" state="visible" r:id="rId3"/>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Không lấy MQTT trực tiếp vào chart để tính #5</t>
   </si>
   <si>
-    <t xml:space="preserve">#3</t>
+    <t xml:space="preserve">#3*</t>
   </si>
   <si>
     <t xml:space="preserve">Web điều khiển LED riêng</t>
@@ -276,10 +276,10 @@
     <t xml:space="preserve">Chứng minh email gửi và nhận</t>
   </si>
   <si>
-    <t xml:space="preserve">#8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatbot truy vấn theo lệnh điều kiện</t>
+    <t xml:space="preserve">#12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chuyển cấu hình Wifi khi lắp đặt</t>
   </si>
   <si>
     <t xml:space="preserve">Lệnh trạng thái/nhiệt độ → trả lời dữ liệu hệ thống</t>
@@ -1324,7 +1324,7 @@
         <v>64</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>65</v>
@@ -1393,7 +1393,7 @@
         <v>79</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>80</v>
